--- a/Documents/SubastUp_API_Endpoints_v3_FINAL.xlsx
+++ b/Documents/SubastUp_API_Endpoints_v3_FINAL.xlsx
@@ -9,18 +9,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="5" max="5" width="62" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="48" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
+    <col min="8" max="8" width="54" customWidth="1"/>
+    <col min="9" max="9" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -93,12 +93,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Healthcheck del backend</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -140,12 +140,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Iniciar sesion y obtener JWT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -187,12 +187,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Registrar usuario pendiente de aprobacion</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -234,12 +234,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Solicitar codigo de recuperacion por email</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -281,12 +281,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Validar codigo de recuperacion y obtener resetToken</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -328,12 +328,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Cambiar contrasena con resetToken</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -375,12 +375,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Si (revisor/admin)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Listar usuarios pendientes de aprobacion</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -422,12 +422,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Si (revisor/admin)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Aprobar o rechazar usuario registrado</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Si (revisor/admin)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Asignar categoria a un usuario</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Cerrar sesion logica</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Obtener perfil del usuario autenticado</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Editar perfil del usuario autenticado</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Historial de pujas del usuario</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Resumen de metricas del usuario</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Evolucion de metricas del usuario</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Productos/subastas del usuario autenticado</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Productos/subastas del usuario</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Articulos confirmados para subasta</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Listar subastas con filtros opcionales</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Calendario de subastas por mes/anio</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Subastas de una fecha especifica</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Sugerencias de busqueda</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Validar imagenes base64 por compatibilidad</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Detalle de subasta</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Link de stream/compartir subasta</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Compatibilidad: cargar producto desde flujo antiguo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Compatibilidad: responder propuesta/estado</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Cargar producto para revision</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Listar productos propios</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Listar articulos propios confirmados</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Si</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Si (revisor/admin)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Listar productos pendientes de revision</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1488,42 +1488,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/api/products/:id/respond</t>
+          <t>/api/products</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Productos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Usuario acepta/rechaza propuesta del revisor</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Listar todos los productos con filtro opcional por estado</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Path: id; Body: action ACCEPT/REJECT, reason?</t>
+          <t>Query: estado?; Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>{ ok, productos }</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>400 action | 404 propuesta</t>
+          <t>401 token | 403 rol</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/api/products/:id/approve</t>
+          <t>/api/products/:id/status</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Revisor/admin aprueba producto y genera propuesta</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Si (revisor/admin)</t>
+          <t>Cambiar estado intermedio del producto</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Path: id; Body: precioBase, comision, fechaSubasta, horaSubasta, lugarSubasta, catalogoId, direccionEnvio?</t>
+          <t>Path: id; Body: estado (pendiente|en_inspeccion)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>{ ok, message, estado }</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>400 datos | 403 rol/empleado | 404 producto</t>
+          <t>400 estado | 401 token | 403 rol | 404 producto</t>
         </is>
       </c>
     </row>
@@ -1587,27 +1587,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/api/products/:id/reject</t>
+          <t>/api/products/:id/respond</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Productos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Revisor/admin rechaza producto</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Si (revisor/admin)</t>
+          <t>Usuario acepta/rechaza propuesta del revisor</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Path: id; Body: motivo, cargo?</t>
+          <t>Path: id; Body: action ACCEPT/REJECT, reason?</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>400 motivo | 403 rol | 404 producto</t>
+          <t>400 action | 404 propuesta</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/api/products/:id</t>
+          <t>/api/products/:id/approve</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Productos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Detalle de producto propio</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Revisor/admin aprueba producto y genera propuesta</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Path: id</t>
+          <t>Path: id; Body: precioBase, comision, fechaSubasta, horaSubasta, lugarSubasta, catalogoId?, direccionEnvio?</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{ ok, producto }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>401 token | 404 producto</t>
+          <t>400 datos | 403 rol/empleado | 404 producto</t>
         </is>
       </c>
     </row>
@@ -1676,32 +1676,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/api/products/:id</t>
+          <t>/api/products/:id/reject</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Productos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eliminar producto propio si esta pendiente</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Revisor/admin rechaza producto</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Path: id</t>
+          <t>Path: id; Body: motivo, cargo?</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>400 estado | 401 token | 404 producto</t>
+          <t>400 motivo | 403 rol | 404 producto</t>
         </is>
       </c>
     </row>
@@ -1728,37 +1728,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/api/bids/:itemId/status</t>
+          <t>/api/products/:id</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pujas</t>
+          <t>Productos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Estado actual de puja de un item</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Detalle de producto propio</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Path: itemId</t>
+          <t>Path: id</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>{ ok, cerrado, pujaActual, tiempoRestante, ... }</t>
+          <t>{ ok, producto }</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>404 item</t>
+          <t>401 token | 404 producto</t>
         </is>
       </c>
     </row>
@@ -1770,42 +1770,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/api/bids</t>
+          <t>/api/products/:id</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pujas</t>
+          <t>Productos</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Realizar puja</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Eliminar producto propio si esta pendiente</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body: auctionId/itemId, amount</t>
+          <t>Path: id</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>201 { ok, message, importeNuevo, tiempoRestante }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>400 negocio | 403 reglas | 404 item | 409 otra subasta</t>
+          <t>400 estado | 401 token | 404 producto</t>
         </is>
       </c>
     </row>
@@ -1822,37 +1822,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/api/chats/unread-count</t>
+          <t>/api/bids/:itemId/status</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Pujas</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cantidad de mensajes no leidos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Estado actual de puja de un item</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Path: itemId</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{ ok, cantidad }</t>
+          <t>{ ok, cerrado, pujaActual, tiempoRestante, ... }</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>401 token</t>
+          <t>404 item</t>
         </is>
       </c>
     </row>
@@ -1864,42 +1864,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/api/chats</t>
+          <t>/api/bids</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Pujas</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Listar conversaciones del usuario</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Realizar puja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Body: auctionId/itemId, amount</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{ ok, conversaciones }</t>
+          <t>201 { ok, message, importeNuevo, tiempoRestante }</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>401 token</t>
+          <t>400 negocio | 403 reglas | 404 item | 409 otra subasta</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/api/chats/:chatId/messages</t>
+          <t>/api/chats/unread-count</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1926,27 +1926,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Obtener mensajes de una conversacion</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Cantidad de mensajes no leidos</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Path: chatId</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{ ok, conversacion, mensajes }</t>
+          <t>{ ok, cantidad }</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>401 token | 404 conversacion</t>
+          <t>401 token</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/api/chats/:chatId/messages</t>
+          <t>/api/chats</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1973,27 +1973,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Enviar mensaje de texto o imagen</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Listar conversaciones del usuario</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Path: chatId; Body: texto?, imagenBase64?</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>201 { ok, message, mensajeId, fecha }</t>
+          <t>{ ok, conversaciones }</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>400 mensaje vacio | 404 conversacion</t>
+          <t>401 token</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/api/chats/create/:productId</t>
+          <t>/api/chats/:chatId/messages</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2020,27 +2020,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crear conversacion para producto</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Si (revisor/admin)</t>
+          <t>Obtener mensajes de una conversacion</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Path: productId; Body: texto</t>
+          <t>Path: chatId</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>201 { ok, message, conversacionId }</t>
+          <t>{ ok, conversacion, mensajes }</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>400 texto | 403 rol | 404 producto | 409 ya existe</t>
+          <t>401 token | 404 conversacion</t>
         </is>
       </c>
     </row>
@@ -2057,37 +2057,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/api/notifications/push-token</t>
+          <t>/api/chats/:chatId/messages</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Notificaciones</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Guardar token push</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Enviar mensaje de texto o imagen</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Body: token</t>
+          <t>Path: chatId; Body: texto?, imagenBase64?</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>201 { ok, message, mensajeId, fecha }</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>400 token | 401 auth</t>
+          <t>400 mensaje vacio | 404 conversacion</t>
         </is>
       </c>
     </row>
@@ -2099,42 +2099,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/api/notifications</t>
+          <t>/api/chats/create/:productId</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Notificaciones</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Listar notificaciones</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Crear conversacion para producto</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Path: productId; Body: texto</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{ ok, notificaciones }</t>
+          <t>201 { ok, message, conversacionId }</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>401 token</t>
+          <t>400 texto | 403 rol | 404 producto | 409 ya existe</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/api/notifications/unread-count</t>
+          <t>/api/notifications/push-token</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2161,27 +2161,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cantidad de notificaciones no leidas</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Guardar token push</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Body: token</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{ ok, total }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>401 token</t>
+          <t>400 token | 401 auth</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/api/notifications/read-all</t>
+          <t>/api/notifications</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marcar todas como leidas</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Listar notificaciones</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>{ ok, notificaciones }</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/api/notifications/:id/read</t>
+          <t>/api/notifications/unread-count</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2255,27 +2255,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marcar notificacion como leida</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Cantidad de notificaciones no leidas</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Path: id</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>{ ok, total }</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>401 token | 404 notificacion</t>
+          <t>401 token</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/api/notifications/subscribe/:auctionId</t>
+          <t>/api/notifications/read-all</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Suscribirse a una subasta</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Marcar todas como leidas</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Path: auctionId</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>201 { ok, message } o 200 si ya estaba</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>401 token | 404 subasta</t>
+          <t>401 token</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/api/notifications/subscribe/:auctionId</t>
+          <t>/api/notifications/:id/read</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cancelar suscripcion a una subasta</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Marcar notificacion como leida</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Path: auctionId</t>
+          <t>Path: id</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>401 token | 404 suscripcion</t>
+          <t>401 token | 404 notificacion</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/api/notifications/:id</t>
+          <t>/api/notifications/subscribe/:auctionId</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2396,27 +2396,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eliminar notificacion</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Suscribirse a una subasta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Path: id</t>
+          <t>Path: auctionId</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>201 { ok, message } o 200 si ya estaba</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>401 token | 404 notificacion</t>
+          <t>401 token | 404 subasta</t>
         </is>
       </c>
     </row>
@@ -2428,42 +2428,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods</t>
+          <t>/api/notifications/subscribe/:auctionId</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Notificaciones</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Listar metodos de pago activos propios</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Cancelar suscripcion a una subasta</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Path: auctionId</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>{ ok, metodos }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>401 token</t>
+          <t>401 token | 404 suscripcion</t>
         </is>
       </c>
     </row>
@@ -2475,42 +2475,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods</t>
+          <t>/api/notifications/:id</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Notificaciones</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agregar metodo de pago generico</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Eliminar notificacion</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Body: tipo + campos del tipo</t>
+          <t>Path: id</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>201 { ok, message, metodoId }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>400 tipo/datos | 401 token</t>
+          <t>401 token | 404 notificacion</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/card</t>
+          <t>/api/settings/payment-methods</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agregar tarjeta</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Listar metodos de pago activos propios</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Body: titular, numeroTarjeta, mesVencimiento, anioVencimiento, codigoSeguridad, direccion?, codigoPostal?, pais?, localidad?</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>201 { ok, message, metodoId }</t>
+          <t>{ ok, metodos }</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>400 datos | 401 token</t>
+          <t>401 token</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/bank</t>
+          <t>/api/settings/payment-methods</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agregar cuenta bancaria</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Agregar metodo de pago generico</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Body: cbu, alias?, titular</t>
+          <t>Body: tipo + campos del tipo</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>400 datos | 401 token</t>
+          <t>400 tipo/datos | 401 token</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/check</t>
+          <t>/api/settings/payment-methods/card</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Agregar cheque</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Agregar tarjeta</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Body: nombreBanco, fechaPago, numeroSucursal?, numeroCheque, imagen?</t>
+          <t>Body: titular, numeroTarjeta, mesVencimiento, anioVencimiento, codigoSeguridad, direccion?, codigoPostal?, pais?, localidad?</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/:id</t>
+          <t>/api/settings/payment-methods/bank</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2678,27 +2678,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eliminar metodo de pago</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Agregar cuenta bancaria</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Path: id</t>
+          <t>Body: cbu, alias?, titular</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>{ ok, message }</t>
+          <t>201 { ok, message, metodoId }</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>401 token | 404 metodo</t>
+          <t>400 datos | 401 token</t>
         </is>
       </c>
     </row>
@@ -2710,42 +2710,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/pending-verification</t>
+          <t>/api/settings/payment-methods/check</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Listar metodos pendientes de verificacion</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Si (revisor/admin)</t>
+          <t>Agregar cheque</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Header: Authorization Bearer token</t>
+          <t>Body: nombreBanco, fechaPago, numeroSucursal?, numeroCheque, imagen?</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>{ ok, metodos }</t>
+          <t>201 { ok, message, metodoId }</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>401 token | 403 rol</t>
+          <t>400 datos | 401 token</t>
         </is>
       </c>
     </row>
@@ -2757,27 +2757,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/api/settings/payment-methods/:id/verify</t>
+          <t>/api/settings/payment-methods/:id</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Verificar metodo de pago</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Si (revisor/admin)</t>
+          <t>Eliminar metodo de pago</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>401 token | 403 rol | 404 metodo</t>
+          <t>401 token | 404 metodo</t>
         </is>
       </c>
     </row>
@@ -2809,37 +2809,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/api/settings</t>
+          <t>/api/settings/payment-methods/pending-verification</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Configuracion</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Obtener configuracion simple</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Listar metodos pendientes de verificacion</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sin body</t>
+          <t>Header: Authorization Bearer token</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>{ ok, settings }</t>
+          <t>{ ok, metodos }</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>500 error interno</t>
+          <t>401 token | 403 rol</t>
         </is>
       </c>
     </row>
@@ -2856,27 +2856,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/api/settings</t>
+          <t>/api/settings/payment-methods/:id/verify</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Configuracion</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Actualizar configuracion simple</t>
+          <t>Si (revisor/admin)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Verificar metodo de pago</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Body libre segun stub</t>
+          <t>Path: id</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>500 error interno</t>
+          <t>401 token | 403 rol | 404 metodo</t>
         </is>
       </c>
     </row>
@@ -2903,22 +2903,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/api/help/faq</t>
+          <t>/api/settings</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Configuracion</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Listar preguntas frecuentes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Obtener configuracion simple</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>{ ok, faq }</t>
+          <t>{ ok, settings }</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2945,42 +2945,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/api/dev/reseed</t>
+          <t>/api/settings</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Desarrollo</t>
+          <t>Configuracion</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reiniciar y cargar datos demo</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DEV_KEY</t>
+          <t>Actualizar configuracion simple</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Query: clave o header x-dev-key</t>
+          <t>Body libre segun stub</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>{ ok, message, resumen, cuentas }</t>
+          <t>{ ok, message }</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>403 clave | 500 reseed</t>
+          <t>500 error interno</t>
         </is>
       </c>
     </row>
@@ -2997,41 +2997,135 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>/api/help/faq</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Listar preguntas frecuentes</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sin body</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>{ ok, faq }</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>500 error interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>/api/dev/reseed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Desarrollo</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DEV_KEY</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Reiniciar y cargar datos demo</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Query: clave o header x-dev-key</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>{ ok, message, resumen, cuentas }</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>403 clave | 500 reseed</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>/api/dev/db</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Desarrollo</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DEV_KEY</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Ver conteos y datos demo sin imagenes</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>DEV_KEY</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Query: clave o header x-dev-key</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>{ ok, counts, usuarios, subastas }</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>403 clave | 500 consulta</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I66"/>
 </worksheet>
 </file>